--- a/drinkcan.xlsx
+++ b/drinkcan.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
@@ -9,12 +9,12 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>Sl No</t>
   </si>
@@ -92,16 +92,25 @@
   </si>
   <si>
     <t>water filter price in bangladesh 2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> water filter stand price in bd</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> water purifier price in bangladesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> water filter price in bangladesh</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -202,10 +211,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -215,7 +222,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -276,7 +285,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -308,10 +317,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -343,7 +351,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -519,9 +526,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:R60"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="5" max="5" width="22.5703125" customWidth="1"/>
     <col min="6" max="6" width="11.42578125" customWidth="1"/>
@@ -535,98 +542,98 @@
     <col min="16" max="16" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:18">
+      <c r="A1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" s="12"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12"/>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="12"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="12"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
-      <c r="M3" s="12"/>
-      <c r="N3" s="12"/>
-      <c r="O3" s="12"/>
-      <c r="P3" s="12"/>
-      <c r="Q3" s="12"/>
-      <c r="R3" s="12"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12"/>
-      <c r="O4" s="12"/>
-      <c r="P4" s="12"/>
-      <c r="Q4" s="12"/>
-      <c r="R4" s="12"/>
-    </row>
-    <row r="5" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+    </row>
+    <row r="2" spans="1:18">
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+    </row>
+    <row r="3" spans="1:18">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+    </row>
+    <row r="4" spans="1:18">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+    </row>
+    <row r="5" spans="1:18" ht="27.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
       <c r="F5" s="1" t="s">
         <v>9</v>
       </c>
@@ -661,146 +668,252 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="8" t="s">
+    <row r="6" spans="1:18" ht="20.100000000000001" customHeight="1">
+      <c r="B6" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="2"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="2">
+        <v>62</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2">
+        <v>3</v>
+      </c>
+      <c r="I6" s="2">
+        <v>10</v>
+      </c>
+      <c r="J6" s="3">
+        <v>2</v>
+      </c>
+      <c r="K6" s="6">
+        <v>2</v>
+      </c>
+      <c r="L6" s="3">
+        <v>2</v>
+      </c>
+      <c r="M6" s="2">
+        <v>968</v>
+      </c>
       <c r="N6" s="3"/>
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
     </row>
-    <row r="7" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="8" t="s">
+    <row r="7" spans="1:18" ht="20.100000000000001" customHeight="1">
+      <c r="B7" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="2">
+        <v>60</v>
+      </c>
+      <c r="G7" s="2">
+        <v>2</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2">
+        <v>8</v>
+      </c>
+      <c r="J7" s="2">
+        <v>1</v>
+      </c>
+      <c r="K7" s="2">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2">
+        <v>1</v>
+      </c>
+      <c r="M7" s="2">
+        <v>136</v>
+      </c>
+      <c r="N7" s="2">
+        <v>2</v>
+      </c>
       <c r="O7" s="4"/>
       <c r="P7" s="4"/>
     </row>
-    <row r="8" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="8" t="s">
+    <row r="8" spans="1:18" ht="20.100000000000001" customHeight="1">
+      <c r="B8" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="2">
+        <v>62</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2">
+        <v>9</v>
+      </c>
+      <c r="J8" s="2">
+        <v>658</v>
+      </c>
+      <c r="K8" s="2">
+        <v>481</v>
+      </c>
+      <c r="L8" s="2">
+        <v>319</v>
+      </c>
+      <c r="M8" s="2">
+        <v>974</v>
+      </c>
       <c r="N8" s="2"/>
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
     </row>
-    <row r="9" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="8" t="s">
+    <row r="9" spans="1:18" ht="20.100000000000001" customHeight="1">
+      <c r="B9" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
       <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
+      <c r="G9" s="2">
+        <v>2</v>
+      </c>
+      <c r="H9" s="2">
+        <v>3</v>
+      </c>
+      <c r="I9" s="2">
+        <v>7</v>
+      </c>
+      <c r="J9" s="2">
+        <v>1680</v>
+      </c>
+      <c r="K9" s="2">
+        <v>1410</v>
+      </c>
+      <c r="L9" s="2">
+        <v>510</v>
+      </c>
+      <c r="M9" s="2">
+        <v>560</v>
+      </c>
       <c r="N9" s="2"/>
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
     </row>
-    <row r="10" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="7" t="s">
+    <row r="10" spans="1:18" ht="20.100000000000001" customHeight="1">
+      <c r="B10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
       <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
+      <c r="G10" s="2">
+        <v>2</v>
+      </c>
+      <c r="H10" s="2">
+        <v>3</v>
+      </c>
+      <c r="I10" s="2">
+        <v>8</v>
+      </c>
+      <c r="J10" s="2">
+        <v>7</v>
+      </c>
+      <c r="K10" s="2">
+        <v>2</v>
+      </c>
+      <c r="L10" s="2">
+        <v>7</v>
+      </c>
+      <c r="M10" s="2">
+        <v>0</v>
+      </c>
       <c r="N10" s="2"/>
       <c r="O10" s="4"/>
       <c r="P10" s="4"/>
     </row>
-    <row r="11" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="7" t="s">
+    <row r="11" spans="1:18" ht="20.100000000000001" customHeight="1">
+      <c r="B11" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
       <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
+      <c r="G11" s="2">
+        <v>1</v>
+      </c>
+      <c r="H11" s="2">
+        <v>3</v>
+      </c>
+      <c r="I11" s="2">
+        <v>4</v>
+      </c>
+      <c r="J11" s="2">
+        <v>153</v>
+      </c>
+      <c r="K11" s="2">
+        <v>52</v>
+      </c>
+      <c r="L11" s="2">
+        <v>63</v>
+      </c>
+      <c r="M11" s="2">
+        <v>949</v>
+      </c>
       <c r="N11" s="2"/>
       <c r="O11" s="4"/>
       <c r="P11" s="4"/>
     </row>
-    <row r="12" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="7" t="s">
+    <row r="12" spans="1:18" ht="20.100000000000001" customHeight="1">
+      <c r="B12" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
       <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
+      <c r="G12" s="2">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2">
+        <v>4</v>
+      </c>
+      <c r="I12" s="2">
+        <v>7</v>
+      </c>
+      <c r="J12" s="2">
+        <v>4360</v>
+      </c>
+      <c r="K12" s="2">
+        <v>1200</v>
+      </c>
+      <c r="L12" s="2">
+        <v>383</v>
+      </c>
+      <c r="M12" s="2">
+        <v>1243</v>
+      </c>
       <c r="N12" s="2"/>
       <c r="O12" s="4"/>
       <c r="P12" s="4"/>
     </row>
-    <row r="13" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="7" t="s">
+    <row r="13" spans="1:18" ht="20.100000000000001" customHeight="1">
+      <c r="B13" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
@@ -812,13 +925,13 @@
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
     </row>
-    <row r="14" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="7" t="s">
+    <row r="14" spans="1:18" ht="20.100000000000001" customHeight="1">
+      <c r="B14" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
@@ -826,343 +939,431 @@
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
-      <c r="M14" s="4"/>
+      <c r="M14" s="4">
+        <v>6117</v>
+      </c>
       <c r="N14" s="2"/>
       <c r="O14" s="5"/>
     </row>
-    <row r="15" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="9" t="s">
+    <row r="15" spans="1:18" ht="20.100000000000001" customHeight="1">
+      <c r="B15" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
       <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
+      <c r="G15" s="2">
+        <v>3</v>
+      </c>
+      <c r="H15" s="2">
+        <v>4</v>
+      </c>
+      <c r="I15" s="2">
+        <v>9</v>
+      </c>
+      <c r="J15" s="2">
+        <v>7</v>
+      </c>
+      <c r="K15" s="2">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2">
+        <v>7</v>
+      </c>
+      <c r="M15" s="2">
+        <v>273</v>
+      </c>
       <c r="N15" s="2"/>
       <c r="O15" s="4"/>
     </row>
-    <row r="16" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="7" t="s">
+    <row r="16" spans="1:18" ht="20.100000000000001" customHeight="1">
+      <c r="B16" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
       <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
+      <c r="G16" s="2">
+        <v>2</v>
+      </c>
+      <c r="H16" s="2">
+        <v>2</v>
+      </c>
+      <c r="I16" s="2">
+        <v>7</v>
+      </c>
+      <c r="J16" s="2">
+        <v>61</v>
+      </c>
+      <c r="K16" s="2">
+        <v>9</v>
+      </c>
+      <c r="L16" s="2">
+        <v>2</v>
+      </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
       <c r="O16" s="4"/>
     </row>
-    <row r="17" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="7" t="s">
+    <row r="17" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B17" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="M17" s="2"/>
-    </row>
-    <row r="18" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-    </row>
-    <row r="19" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-    </row>
-    <row r="20" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-    </row>
-    <row r="21" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-    </row>
-    <row r="22" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-    </row>
-    <row r="23" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-    </row>
-    <row r="24" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-    </row>
-    <row r="25" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-    </row>
-    <row r="26" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-    </row>
-    <row r="27" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-    </row>
-    <row r="28" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-    </row>
-    <row r="29" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-    </row>
-    <row r="30" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-    </row>
-    <row r="31" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-    </row>
-    <row r="32" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-    </row>
-    <row r="33" spans="2:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-    </row>
-    <row r="34" spans="2:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-    </row>
-    <row r="35" spans="2:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-    </row>
-    <row r="36" spans="2:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-    </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-    </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-    </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-    </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-    </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-    </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-    </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-    </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-    </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-    </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-    </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-    </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-    </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-    </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-    </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-    </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-    </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-    </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-    </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-    </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-    </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-    </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="M17" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B18" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="G18">
+        <v>3</v>
+      </c>
+      <c r="H18">
+        <v>3</v>
+      </c>
+      <c r="I18">
+        <v>7</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B19" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="G19">
+        <v>2</v>
+      </c>
+      <c r="H19">
+        <v>2</v>
+      </c>
+      <c r="I19">
+        <v>7</v>
+      </c>
+      <c r="J19">
+        <v>1680</v>
+      </c>
+      <c r="K19">
+        <v>510</v>
+      </c>
+      <c r="L19">
+        <v>1410</v>
+      </c>
+      <c r="M19">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B20" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="G20">
+        <v>2</v>
+      </c>
+      <c r="H20">
+        <v>2</v>
+      </c>
+      <c r="I20">
+        <v>7</v>
+      </c>
+      <c r="J20">
+        <v>658</v>
+      </c>
+      <c r="K20">
+        <v>481</v>
+      </c>
+      <c r="L20">
+        <v>319</v>
+      </c>
+      <c r="M20">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+    </row>
+    <row r="22" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+    </row>
+    <row r="23" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+    </row>
+    <row r="24" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+    </row>
+    <row r="25" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+    </row>
+    <row r="26" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+    </row>
+    <row r="27" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+    </row>
+    <row r="28" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+    </row>
+    <row r="29" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+    </row>
+    <row r="30" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+    </row>
+    <row r="31" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+    </row>
+    <row r="32" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+    </row>
+    <row r="33" spans="2:5" ht="20.100000000000001" customHeight="1">
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+    </row>
+    <row r="34" spans="2:5" ht="20.100000000000001" customHeight="1">
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+    </row>
+    <row r="35" spans="2:5" ht="20.100000000000001" customHeight="1">
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+    </row>
+    <row r="36" spans="2:5" ht="20.100000000000001" customHeight="1">
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+    </row>
+    <row r="37" spans="2:5">
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+    </row>
+    <row r="38" spans="2:5">
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+    </row>
+    <row r="39" spans="2:5">
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+    </row>
+    <row r="40" spans="2:5">
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+    </row>
+    <row r="41" spans="2:5">
+      <c r="B41" s="8"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+    </row>
+    <row r="42" spans="2:5">
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+    </row>
+    <row r="43" spans="2:5">
+      <c r="B43" s="7"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
+    </row>
+    <row r="44" spans="2:5">
+      <c r="B44" s="7"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="7"/>
+    </row>
+    <row r="45" spans="2:5">
+      <c r="B45" s="7"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+    </row>
+    <row r="46" spans="2:5">
+      <c r="B46" s="7"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
+    </row>
+    <row r="47" spans="2:5">
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7"/>
+    </row>
+    <row r="48" spans="2:5">
+      <c r="B48" s="7"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
+    </row>
+    <row r="49" spans="2:5">
+      <c r="B49" s="7"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
+    </row>
+    <row r="50" spans="2:5">
+      <c r="B50" s="7"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="7"/>
+    </row>
+    <row r="51" spans="2:5">
+      <c r="B51" s="7"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
+    </row>
+    <row r="52" spans="2:5">
+      <c r="B52" s="7"/>
+      <c r="C52" s="7"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
+    </row>
+    <row r="53" spans="2:5">
+      <c r="B53" s="7"/>
+      <c r="C53" s="7"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
+    </row>
+    <row r="54" spans="2:5">
+      <c r="B54" s="7"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
+    </row>
+    <row r="55" spans="2:5">
+      <c r="B55" s="7"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+    </row>
+    <row r="56" spans="2:5">
+      <c r="B56" s="7"/>
+      <c r="C56" s="7"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="7"/>
+    </row>
+    <row r="57" spans="2:5">
+      <c r="B57" s="7"/>
+      <c r="C57" s="7"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
+    </row>
+    <row r="58" spans="2:5">
+      <c r="B58" s="7"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
+    </row>
+    <row r="59" spans="2:5">
+      <c r="B59" s="7"/>
+      <c r="C59" s="7"/>
+      <c r="D59" s="7"/>
+      <c r="E59" s="7"/>
+    </row>
+    <row r="60" spans="2:5">
+      <c r="B60" s="7"/>
+      <c r="C60" s="7"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="57">
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="B60:E60"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="B54:E54"/>
-    <mergeCell ref="B55:E55"/>
-    <mergeCell ref="B56:E56"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="A1:R4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B31:E31"/>
     <mergeCell ref="B20:E20"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B10:E10"/>
@@ -1175,23 +1376,34 @@
     <mergeCell ref="B17:E17"/>
     <mergeCell ref="B18:E18"/>
     <mergeCell ref="B19:E19"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="A1:R4"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="B55:E55"/>
+    <mergeCell ref="B56:E56"/>
+    <mergeCell ref="B57:E57"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/drinkcan.xlsx
+++ b/drinkcan.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
@@ -202,10 +202,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -215,7 +213,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -276,7 +276,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -311,7 +311,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -536,97 +536,97 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" s="12"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12"/>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="12"/>
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="12"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
-      <c r="M3" s="12"/>
-      <c r="N3" s="12"/>
-      <c r="O3" s="12"/>
-      <c r="P3" s="12"/>
-      <c r="Q3" s="12"/>
-      <c r="R3" s="12"/>
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12"/>
-      <c r="O4" s="12"/>
-      <c r="P4" s="12"/>
-      <c r="Q4" s="12"/>
-      <c r="R4" s="12"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
     </row>
     <row r="5" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
       <c r="F5" s="1" t="s">
         <v>9</v>
       </c>
@@ -662,12 +662,12 @@
       </c>
     </row>
     <row r="6" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -681,12 +681,12 @@
       <c r="P6" s="4"/>
     </row>
     <row r="7" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -700,12 +700,12 @@
       <c r="P7" s="4"/>
     </row>
     <row r="8" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
@@ -719,12 +719,12 @@
       <c r="P8" s="4"/>
     </row>
     <row r="9" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
@@ -738,12 +738,12 @@
       <c r="P9" s="4"/>
     </row>
     <row r="10" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -757,12 +757,12 @@
       <c r="P10" s="4"/>
     </row>
     <row r="11" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
@@ -776,12 +776,12 @@
       <c r="P11" s="4"/>
     </row>
     <row r="12" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -795,12 +795,12 @@
       <c r="P12" s="4"/>
     </row>
     <row r="13" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
@@ -813,12 +813,12 @@
       <c r="O13" s="2"/>
     </row>
     <row r="14" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
@@ -831,12 +831,12 @@
       <c r="O14" s="5"/>
     </row>
     <row r="15" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
@@ -849,12 +849,12 @@
       <c r="O15" s="4"/>
     </row>
     <row r="16" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
@@ -867,302 +867,291 @@
       <c r="O16" s="4"/>
     </row>
     <row r="17" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
       <c r="M17" s="2"/>
     </row>
     <row r="18" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
     </row>
     <row r="19" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
     </row>
     <row r="20" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
     </row>
     <row r="21" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
     </row>
     <row r="22" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
     </row>
     <row r="23" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
     </row>
     <row r="24" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
     </row>
     <row r="25" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
     </row>
     <row r="26" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
     </row>
     <row r="27" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
     </row>
     <row r="28" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
     </row>
     <row r="29" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
     </row>
     <row r="30" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
     </row>
     <row r="31" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
     </row>
     <row r="32" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
     </row>
     <row r="33" spans="2:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
     </row>
     <row r="34" spans="2:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
     </row>
     <row r="35" spans="2:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
     </row>
     <row r="36" spans="2:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
+      <c r="B43" s="7"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
+      <c r="B44" s="7"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="7"/>
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
+      <c r="B46" s="7"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7"/>
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
+      <c r="B48" s="7"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
+      <c r="B49" s="7"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
+      <c r="B50" s="7"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="7"/>
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
+      <c r="B51" s="7"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
+      <c r="B52" s="7"/>
+      <c r="C52" s="7"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
+      <c r="B53" s="7"/>
+      <c r="C53" s="7"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
     </row>
     <row r="54" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
+      <c r="B54" s="7"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
+      <c r="B55" s="7"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
+      <c r="B56" s="7"/>
+      <c r="C56" s="7"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="7"/>
     </row>
     <row r="57" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
+      <c r="B57" s="7"/>
+      <c r="C57" s="7"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
+      <c r="B58" s="7"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
+      <c r="B59" s="7"/>
+      <c r="C59" s="7"/>
+      <c r="D59" s="7"/>
+      <c r="E59" s="7"/>
     </row>
     <row r="60" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
+      <c r="B60" s="7"/>
+      <c r="C60" s="7"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="57">
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="B60:E60"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="B54:E54"/>
-    <mergeCell ref="B55:E55"/>
-    <mergeCell ref="B56:E56"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="A1:R4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B31:E31"/>
     <mergeCell ref="B20:E20"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B10:E10"/>
@@ -1175,23 +1164,34 @@
     <mergeCell ref="B17:E17"/>
     <mergeCell ref="B18:E18"/>
     <mergeCell ref="B19:E19"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="A1:R4"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="B55:E55"/>
+    <mergeCell ref="B56:E56"/>
+    <mergeCell ref="B57:E57"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
